--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487724_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487724_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.065099999999999</v>
+        <v>7.9255</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6396</v>
+        <v>3.4999</v>
       </c>
       <c r="F2" t="n">
         <v>4.4255</v>
@@ -610,10 +610,10 @@
         <v>2.7164</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0738</v>
+        <v>1.9342</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4692</v>
+        <v>1.3296</v>
       </c>
       <c r="U2" t="n">
         <v>0.6046</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.2803</v>
+        <v>6.1792</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5533</v>
+        <v>3.4522</v>
       </c>
       <c r="F3" t="n">
         <v>2.727</v>
@@ -688,10 +688,10 @@
         <v>2.1344</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4506</v>
+        <v>1.3495</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1848</v>
+        <v>1.0837</v>
       </c>
       <c r="U3" t="n">
         <v>0.2658</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0211</v>
+        <v>4.655</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7353</v>
+        <v>2.3965</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2858</v>
+        <v>2.2586</v>
       </c>
       <c r="G4" t="n">
         <v>2.1779</v>
@@ -766,13 +766,13 @@
         <v>2.5224</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2615</v>
+        <v>0.3724</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5451</v>
+        <v>0.1161</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2836</v>
+        <v>0.2563</v>
       </c>
       <c r="V4" t="n">
         <v>2.8809</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. ATIENZA PEREA</t>
+          <t>J. DOMINGUEZ LARRE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6927</v>
+        <v>3.9579</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4036</v>
+        <v>1.4575</v>
       </c>
       <c r="F5" t="n">
-        <v>4.0963</v>
+        <v>2.5004</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.099</v>
+        <v>2.0065</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2669</v>
+        <v>0.337</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3659</v>
+        <v>1.6695</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.1819</v>
+        <v>2.6092</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5602</v>
+        <v>0.795</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6217</v>
+        <v>1.8141</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0829</v>
+        <v>-0.6027</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8270999999999999</v>
+        <v>-0.4581</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2558</v>
+        <v>-0.1446</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9403</v>
+        <v>0.3881</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.3881</v>
+        <v>-2.3284</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3284</v>
+        <v>2.7164</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4737</v>
+        <v>0.1884</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1664</v>
+        <v>-0.0471</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3073</v>
+        <v>0.2355</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3776</v>
+        <v>1.3749</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3776</v>
+        <v>0.1511</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ LARRE</t>
+          <t>J. ATIENZA PEREA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.6853</v>
+        <v>3.1165</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4575</v>
+        <v>-0.8435</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2278</v>
+        <v>3.96</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0065</v>
+        <v>-0.099</v>
       </c>
       <c r="H6" t="n">
-        <v>0.337</v>
+        <v>0.2669</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6695</v>
+        <v>-0.3659</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6092</v>
+        <v>-1.1819</v>
       </c>
       <c r="K6" t="n">
-        <v>0.795</v>
+        <v>-0.5602</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8141</v>
+        <v>-0.6217</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6027</v>
+        <v>1.0829</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4581</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1446</v>
+        <v>0.2558</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3881</v>
+        <v>1.9403</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.3284</v>
+        <v>-0.3881</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7164</v>
+        <v>2.3284</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.08409999999999999</v>
+        <v>0.8975</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0471</v>
+        <v>0.7265</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.037</v>
+        <v>0.1711</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3749</v>
+        <v>0.3776</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1511</v>
+        <v>0.3776</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5514</v>
+        <v>1.6059</v>
       </c>
       <c r="E7" t="n">
         <v>0.86</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6913</v>
+        <v>0.7458</v>
       </c>
       <c r="G7" t="n">
         <v>0.9054</v>
@@ -1000,13 +1000,13 @@
         <v>0.3881</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0242</v>
+        <v>0.0303</v>
       </c>
       <c r="T7" t="n">
         <v>-0.0606</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>0.2821</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6203</v>
+        <v>1.163</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7301</v>
+        <v>1.1911</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1098</v>
+        <v>-0.0281</v>
       </c>
       <c r="G8" t="n">
         <v>0.08409999999999999</v>
@@ -1078,13 +1078,13 @@
         <v>1.7463</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5399</v>
+        <v>0.0028</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2299</v>
+        <v>0.231</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.31</v>
+        <v>-0.2282</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2821</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.361</v>
+        <v>-0.2057</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.5076</v>
+        <v>-3.7473</v>
       </c>
       <c r="F9" t="n">
-        <v>3.8686</v>
+        <v>3.5416</v>
       </c>
       <c r="G9" t="n">
         <v>-3.8279</v>
@@ -1156,13 +1156,13 @@
         <v>3.4926</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5036</v>
+        <v>0.9368</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7907</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7129</v>
+        <v>0.3859</v>
       </c>
       <c r="V9" t="n">
         <v>1.3271</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. SIMON DEL CORRAL</t>
+          <t>D. FERNANDEZ CAÑAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6538</v>
+        <v>-0.3923</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6074</v>
+        <v>-2.1586</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9535</v>
+        <v>1.7664</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6117</v>
+        <v>-1.2957</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1534</v>
+        <v>-0.7852</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4582</v>
+        <v>-0.5105</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1711</v>
+        <v>-1.7778</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5849</v>
+        <v>-0.6055</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5861</v>
+        <v>-1.1723</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4406</v>
+        <v>0.4821</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5685</v>
+        <v>-0.1796</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1279</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1642</v>
+        <v>1.3582</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.194</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3582</v>
+        <v>1.5523</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2064</v>
+        <v>-0.1727</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2423</v>
+        <v>-0.1868</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0359</v>
+        <v>0.014</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ CAÑAS</t>
+          <t>A. SIMON DEL CORRAL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9656</v>
+        <v>-0.4536</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7592</v>
+        <v>-1.4072</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7936</v>
+        <v>0.9535</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2957</v>
+        <v>-1.6117</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7852</v>
+        <v>-1.1534</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5105</v>
+        <v>-0.4582</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.7778</v>
+        <v>-1.1711</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6055</v>
+        <v>-0.5849</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.1723</v>
+        <v>-0.5861</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4821</v>
+        <v>-0.4406</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1796</v>
+        <v>-0.5685</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.1279</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3582</v>
+        <v>1.1642</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.194</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5523</v>
+        <v>1.3582</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7461</v>
+        <v>-0.0062</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7874</v>
+        <v>-0.0421</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0413</v>
+        <v>0.0359</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7096</v>
+        <v>-1.4821</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7538</v>
+        <v>-1.5536</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0442</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-1.4154</v>
@@ -1390,13 +1390,13 @@
         <v>0.9702</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3822</v>
+        <v>-0.1548</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1694</v>
+        <v>0.0308</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2129</v>
+        <v>-0.1856</v>
       </c>
       <c r="V12" t="n">
         <v>0.2821</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.8008</v>
+        <v>-1.6189</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1884</v>
+        <v>0.2885</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9892</v>
+        <v>-1.9074</v>
       </c>
       <c r="G13" t="n">
         <v>0.0264</v>
@@ -1468,13 +1468,13 @@
         <v>0.3881</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7093</v>
+        <v>-0.5274</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4845</v>
+        <v>-0.3844</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2248</v>
+        <v>-0.143</v>
       </c>
       <c r="V13" t="n">
         <v>-1.506</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>24.1474</v>
+        <v>24.4504</v>
       </c>
       <c r="E14" t="n">
-        <v>3.132599999999999</v>
+        <v>3.435500000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>21.0146</v>
+        <v>21.0148</v>
       </c>
       <c r="G14" t="n">
-        <v>4.117299999999998</v>
+        <v>4.1173</v>
       </c>
       <c r="H14" t="n">
         <v>6.730900000000002</v>
@@ -1522,19 +1522,19 @@
         <v>4.050999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>7.192600000000001</v>
+        <v>7.192600000000002</v>
       </c>
       <c r="L14" t="n">
-        <v>-3.1417</v>
+        <v>-3.141699999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>0.06640000000000001</v>
+        <v>0.06640000000000046</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4615999999999998</v>
+        <v>-0.4616</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5282000000000002</v>
+        <v>0.5282</v>
       </c>
       <c r="P14" t="n">
         <v>7.7614</v>
@@ -1546,13 +1546,13 @@
         <v>22.3138</v>
       </c>
       <c r="S14" t="n">
-        <v>4.548</v>
+        <v>4.8508</v>
       </c>
       <c r="T14" t="n">
-        <v>3.0448</v>
+        <v>3.3476</v>
       </c>
       <c r="U14" t="n">
-        <v>1.503</v>
+        <v>1.5031</v>
       </c>
       <c r="V14" t="n">
         <v>7.720800000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9789</v>
+        <v>0.8153</v>
       </c>
       <c r="E15" t="n">
         <v>-0.8124</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7913</v>
+        <v>1.6278</v>
       </c>
       <c r="G15" t="n">
         <v>-0.3791</v>
@@ -1624,13 +1624,13 @@
         <v>1.1642</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5819</v>
+        <v>0.4183</v>
       </c>
       <c r="T15" t="n">
         <v>-0.0471</v>
       </c>
       <c r="U15" t="n">
-        <v>0.629</v>
+        <v>0.4655</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7827</v>
+        <v>0.7977</v>
       </c>
       <c r="E16" t="n">
-        <v>2.584</v>
+        <v>2.3838</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8013</v>
+        <v>-1.5861</v>
       </c>
       <c r="G16" t="n">
         <v>2.5261</v>
@@ -1702,13 +1702,13 @@
         <v>2.7164</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8181</v>
+        <v>-0.8031</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2568</v>
+        <v>0.0566</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0749</v>
+        <v>-0.8597</v>
       </c>
       <c r="V16" t="n">
         <v>-3.0597</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.754</v>
+        <v>0.5087</v>
       </c>
       <c r="E17" t="n">
         <v>-1.1833</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9373</v>
+        <v>1.692</v>
       </c>
       <c r="G17" t="n">
         <v>0.16</v>
@@ -1780,13 +1780,13 @@
         <v>1.7463</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0119</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="T17" t="n">
         <v>0.1346</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8773</v>
+        <v>0.632</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6119</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. ABOUBACAR HIMA</t>
+          <t>J. FRANCES PASCUAL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2498</v>
+        <v>-0.7748</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2867</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0369</v>
+        <v>-0.2601</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8352000000000001</v>
+        <v>-0.2353</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9615</v>
+        <v>-1.2852</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1263</v>
+        <v>1.0499</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5936</v>
+        <v>-0.0178</v>
       </c>
       <c r="K18" t="n">
-        <v>1.553</v>
+        <v>-0.6673</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0406</v>
+        <v>0.6495</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7584</v>
+        <v>-0.2175</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5916</v>
+        <v>-0.6179</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1669</v>
+        <v>0.4004</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.1344</v>
+        <v>-0.194</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.8806</v>
+        <v>-0.194</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7463</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4852</v>
+        <v>-0.3454</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1541</v>
+        <v>-0.3028</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6689000000000001</v>
+        <v>-0.0426</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5642</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8462</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. FRANCES PASCUAL</t>
+          <t>S. ABOUBACAR HIMA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8293</v>
+        <v>-1.1719</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-1.2877</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3146</v>
+        <v>0.1158</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2353</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2852</v>
+        <v>0.9615</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0499</v>
+        <v>-0.1263</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0178</v>
+        <v>1.5936</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6673</v>
+        <v>1.553</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6495</v>
+        <v>0.0406</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2175</v>
+        <v>-0.7584</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6179</v>
+        <v>-0.5916</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4004</v>
+        <v>-0.1669</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.194</v>
+        <v>-2.1344</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.194</v>
+        <v>-3.8806</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.7463</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4</v>
+        <v>-0.4368</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3028</v>
+        <v>0.1531</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.5899</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.8462</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. BALDAN MARTÍN</t>
+          <t>V. ALONSO PASCUAL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5544</v>
+        <v>-2.4478</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9216</v>
+        <v>-0.602</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6328</v>
+        <v>-1.8458</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.229</v>
+        <v>1.3267</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4226</v>
+        <v>-1.7886</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8064</v>
+        <v>3.1153</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6055</v>
+        <v>1.0123</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0618</v>
+        <v>-0.9186</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6673</v>
+        <v>1.9309</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6235000000000001</v>
+        <v>0.3145</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4844</v>
+        <v>-0.87</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.139</v>
+        <v>1.1845</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.7463</v>
+        <v>1.1642</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1344</v>
+        <v>-1.3582</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3881</v>
+        <v>2.5224</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.297</v>
+        <v>-1.2671</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1817</v>
+        <v>-0.256</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1153</v>
+        <v>-1.0111</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2821</v>
+        <v>-3.6716</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2821</v>
+        <v>-3.6716</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V. ALONSO PASCUAL</t>
+          <t>M. BALDAN MARTÍN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6363</v>
+        <v>-3.427</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3027</v>
+        <v>-2.8215</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3336</v>
+        <v>-0.6055</v>
       </c>
       <c r="G21" t="n">
-        <v>1.3267</v>
+        <v>-1.229</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7886</v>
+        <v>-0.4226</v>
       </c>
       <c r="I21" t="n">
-        <v>3.1153</v>
+        <v>-0.8064</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0123</v>
+        <v>-0.6055</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9186</v>
+        <v>0.0618</v>
       </c>
       <c r="L21" t="n">
-        <v>1.9309</v>
+        <v>-0.6673</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3145</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.87</v>
+        <v>-0.4844</v>
       </c>
       <c r="O21" t="n">
-        <v>1.1845</v>
+        <v>-0.139</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1642</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.3582</v>
+        <v>-2.1344</v>
       </c>
       <c r="R21" t="n">
-        <v>2.5224</v>
+        <v>0.3881</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.4556</v>
+        <v>-0.1696</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9567</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.4988</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.6716</v>
+        <v>-0.2821</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.6716</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.907</v>
+        <v>-3.7251</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7082</v>
+        <v>-2.6081</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1988</v>
+        <v>-1.117</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1546</v>
@@ -2170,13 +2170,13 @@
         <v>0.3881</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1702</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.424</v>
+        <v>-0.3239</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7463</v>
+        <v>-0.6645</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.8051</v>
+        <v>-5.9075</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.3518</v>
+        <v>-5.7512</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4533</v>
+        <v>-0.1563</v>
       </c>
       <c r="G23" t="n">
         <v>-1.4712</v>
@@ -2248,13 +2248,13 @@
         <v>1.3582</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.9771</v>
+        <v>-1.0795</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0173</v>
+        <v>-0.4167</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9598</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>0.3299</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.6813</v>
+        <v>-8.1479</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.5175</v>
+        <v>-7.8178</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1638</v>
+        <v>-0.3302</v>
       </c>
       <c r="G24" t="n">
         <v>-3.4961</v>
@@ -2326,13 +2326,13 @@
         <v>2.5224</v>
       </c>
       <c r="S24" t="n">
-        <v>0.491</v>
+        <v>0.0244</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1189</v>
+        <v>-0.4192</v>
       </c>
       <c r="U24" t="n">
-        <v>0.61</v>
+        <v>0.4436</v>
       </c>
       <c r="V24" t="n">
         <v>-0.9896</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-24.1476</v>
+        <v>-23.4803</v>
       </c>
       <c r="E25" t="n">
         <v>-21.0148</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.1327</v>
+        <v>-2.465400000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-4.1173</v>
@@ -2383,7 +2383,7 @@
         <v>0.4615</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5279999999999999</v>
+        <v>-0.5279999999999997</v>
       </c>
       <c r="M25" t="n">
         <v>-4.0508</v>
@@ -2404,13 +2404,13 @@
         <v>14.5524</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.548</v>
+        <v>-3.8806</v>
       </c>
       <c r="T25" t="n">
         <v>-1.503</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.0448</v>
+        <v>-2.3775</v>
       </c>
       <c r="V25" t="n">
         <v>-7.7208</v>
